--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -33799,12 +33799,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -33829,12 +33829,12 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N201" t="n">
@@ -33877,42 +33877,42 @@
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33944,12 +33944,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -34022,40 +34022,185 @@
       </c>
       <c r="AV202" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
+      <c r="AT203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW202" t="inlineStr">
+      <c r="AW203" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX202" t="inlineStr">
+      <c r="AX203" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY202" t="inlineStr">
+      <c r="AY203" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ202" t="inlineStr">
+      <c r="AZ203" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA202" t="inlineStr">
+      <c r="BA203" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB202" t="inlineStr">
+      <c r="BB203" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC202" t="inlineStr">
+      <c r="BC203" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -34177,7 +34322,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10">
@@ -34187,7 +34332,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -31498,12 +31498,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -31537,13 +31537,16 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O188" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q188" t="n">
         <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>0.0002123271347081624</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -31576,42 +31579,42 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -31643,12 +31646,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -31673,7 +31676,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -31721,42 +31724,42 @@
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31788,12 +31791,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -31832,9 +31835,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -31843,77 +31843,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31940,7 +31931,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -31992,98 +31983,18 @@
       <c r="P191" t="n">
         <v>0</v>
       </c>
-      <c r="U191" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W191" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y191" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R191" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD191" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE191" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF191" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG191" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN191" t="b">
-        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
@@ -32177,17 +32088,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -32212,7 +32123,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -32226,76 +32137,168 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN192" t="b">
+        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32327,12 +32330,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -32371,9 +32374,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="P193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -32382,77 +32382,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32479,7 +32470,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -32531,98 +32522,18 @@
       <c r="P194" t="n">
         <v>0</v>
       </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN194" t="b">
-        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -32716,17 +32627,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -32751,7 +32662,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -32765,76 +32676,168 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="R195" t="n">
-        <v>0</v>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
+        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32866,12 +32869,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -32910,9 +32913,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="P196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -32921,77 +32921,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33018,7 +33009,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -33070,98 +33061,18 @@
       <c r="P197" t="n">
         <v>0</v>
       </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD197" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE197" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN197" t="b">
-        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
@@ -33255,17 +33166,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -33290,7 +33201,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -33299,81 +33210,173 @@
         </is>
       </c>
       <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN198" t="b">
         <v>1</v>
       </c>
-      <c r="O198" t="n">
-        <v>1</v>
-      </c>
-      <c r="R198" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33405,12 +33408,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -33444,93 +33447,81 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O199" t="n">
-        <v>0</v>
-      </c>
-      <c r="P199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33557,7 +33548,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -33609,98 +33600,18 @@
       <c r="P200" t="n">
         <v>0</v>
       </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -33794,17 +33705,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -33829,7 +33740,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -33843,76 +33754,168 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="R201" t="n">
-        <v>0</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33944,12 +33947,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -33974,12 +33977,12 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N202" t="n">
@@ -34022,42 +34025,42 @@
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34089,118 +34092,657 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>1</v>
+      </c>
+      <c r="O203" t="n">
+        <v>1</v>
+      </c>
+      <c r="P203" t="n">
+        <v>1</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA203" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>1</v>
+      </c>
+      <c r="O204" t="n">
+        <v>1</v>
+      </c>
+      <c r="P204" t="n">
+        <v>1</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV204" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA204" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB204" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC204" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
+      <c r="AT205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA205" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB205" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC205" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="G206" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>D002</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
         <is>
           <t>霍乱</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="K206" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
+      <c r="L206" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr">
+      <c r="M206" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N203" t="n">
-        <v>0</v>
-      </c>
-      <c r="O203" t="n">
-        <v>0</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0</v>
-      </c>
-      <c r="S203" t="inlineStr">
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO203" t="inlineStr">
+      <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP203" t="inlineStr">
+      <c r="AP206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR203" t="inlineStr">
+      <c r="AR206" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS203" t="inlineStr"/>
-      <c r="AT203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU203" t="inlineStr">
+      <c r="AS206" t="inlineStr"/>
+      <c r="AT206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU206" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV203" t="inlineStr">
+      <c r="AV206" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW203" t="inlineStr">
+      <c r="AW206" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX203" t="inlineStr">
+      <c r="AX206" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY203" t="inlineStr">
+      <c r="AY206" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ203" t="inlineStr">
+      <c r="AZ206" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA203" t="inlineStr">
+      <c r="BA206" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB203" t="inlineStr">
+      <c r="BB206" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC203" t="inlineStr">
+      <c r="BC206" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -34322,7 +34864,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
@@ -34332,7 +34874,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -34352,7 +34894,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -34384,7 +34926,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -26898,12 +26898,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -26937,84 +26937,92 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0.0002831028462775499</v>
+        <v>0</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27041,17 +27049,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27090,76 +27098,165 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary cholera notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>1</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27191,12 +27288,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27230,13 +27327,16 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O161" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q161" t="n">
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>0.0002831028462775499</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27269,42 +27369,42 @@
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -27336,12 +27436,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27366,7 +27466,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -27414,42 +27514,42 @@
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -27481,12 +27581,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27511,7 +27611,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -27559,42 +27659,42 @@
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27626,12 +27726,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27656,7 +27756,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -27670,9 +27770,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="P164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -27681,77 +27778,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27778,17 +27866,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -27813,7 +27901,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -27827,168 +27915,76 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="P165" t="n">
-        <v>0</v>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN165" t="b">
-        <v>1</v>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28020,12 +28016,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28050,7 +28046,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -28064,6 +28060,9 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -28072,68 +28071,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28160,17 +28168,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -28195,7 +28203,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -28209,76 +28217,168 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="R167" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28310,12 +28410,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -28340,7 +28440,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -28354,9 +28454,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -28365,77 +28462,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28462,17 +28550,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -28497,7 +28585,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -28511,168 +28599,76 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="P169" t="n">
-        <v>0</v>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE169" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF169" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG169" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN169" t="b">
-        <v>1</v>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28704,12 +28700,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -28734,7 +28730,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -28748,6 +28744,9 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -28756,68 +28755,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28844,17 +28852,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -28879,7 +28887,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -28893,76 +28901,168 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="R171" t="n">
-        <v>0</v>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>1</v>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28994,12 +29094,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -29024,7 +29124,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -29038,9 +29138,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="P172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -29049,77 +29146,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ172" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29146,17 +29234,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -29181,7 +29269,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -29195,168 +29283,76 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="P173" t="n">
-        <v>0</v>
-      </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V173" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W173" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD173" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE173" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF173" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG173" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH173" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI173" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ173" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK173" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM173" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN173" t="b">
-        <v>1</v>
+      <c r="R173" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29388,12 +29384,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -29418,7 +29414,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -29432,6 +29428,9 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -29440,68 +29439,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29528,17 +29536,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -29563,7 +29571,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -29577,76 +29585,168 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="R175" t="n">
-        <v>0</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN175" t="b">
+        <v>1</v>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29708,7 +29808,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -29823,12 +29923,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -29853,7 +29953,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -29867,9 +29967,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="P177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -29878,77 +29975,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29975,17 +30063,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -30024,168 +30112,76 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="P178" t="n">
-        <v>0</v>
-      </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE178" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF178" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG178" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ178" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM178" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN178" t="b">
-        <v>1</v>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30217,12 +30213,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -30247,12 +30243,12 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N179" t="n">
@@ -30261,6 +30257,9 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -30269,68 +30268,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30357,17 +30365,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -30392,12 +30400,12 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N180" t="n">
@@ -30406,73 +30414,168 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN180" t="b">
+        <v>1</v>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30504,12 +30607,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -30548,9 +30651,12 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -30584,12 +30690,12 @@
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -30604,12 +30710,12 @@
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
@@ -30646,12 +30752,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -30726,7 +30832,7 @@
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
@@ -30746,7 +30852,7 @@
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
@@ -30788,12 +30894,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -30868,7 +30974,7 @@
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
@@ -30888,7 +30994,7 @@
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
@@ -30930,12 +31036,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -31010,7 +31116,7 @@
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
@@ -31030,7 +31136,7 @@
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
@@ -31072,12 +31178,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -31152,7 +31258,7 @@
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
@@ -31172,7 +31278,7 @@
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
@@ -31214,12 +31320,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -31294,7 +31400,7 @@
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
@@ -31314,7 +31420,7 @@
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
@@ -31356,12 +31462,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -31436,7 +31542,7 @@
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
@@ -31456,7 +31562,7 @@
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
@@ -31498,12 +31604,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -31537,20 +31643,14 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0.0002123271347081624</v>
+        <v>0</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -31579,42 +31679,42 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31646,12 +31746,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -31690,12 +31790,9 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="R189" t="n">
-        <v>0</v>
-      </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
@@ -31724,42 +31821,42 @@
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31791,12 +31888,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -31821,7 +31918,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -31830,13 +31927,16 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O190" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q190" t="n">
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>0.0002123271347081624</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -31869,17 +31969,17 @@
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -31889,22 +31989,22 @@
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -31936,12 +32036,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -31966,7 +32066,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -31980,9 +32080,6 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="P191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -31991,77 +32088,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -32088,17 +32176,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -32137,168 +32225,76 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="P192" t="n">
-        <v>0</v>
-      </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA192" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
-        <v>1</v>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32330,12 +32326,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -32360,7 +32356,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -32374,6 +32370,9 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -32382,68 +32381,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32470,7 +32478,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -32505,7 +32513,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -32522,18 +32530,98 @@
       <c r="P194" t="n">
         <v>0</v>
       </c>
-      <c r="R194" t="n">
-        <v>0</v>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -32627,17 +32715,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -32676,168 +32764,76 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="P195" t="n">
-        <v>0</v>
-      </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN195" t="b">
-        <v>1</v>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32869,12 +32865,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -32899,7 +32895,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -32913,6 +32909,9 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -32921,68 +32920,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33017,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -33044,7 +33052,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -33061,18 +33069,98 @@
       <c r="P197" t="n">
         <v>0</v>
       </c>
-      <c r="R197" t="n">
-        <v>0</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
@@ -33166,17 +33254,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -33215,168 +33303,76 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="P198" t="n">
-        <v>0</v>
-      </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>1</v>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33408,12 +33404,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -33438,7 +33434,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -33447,81 +33443,93 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33548,7 +33556,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -33583,7 +33591,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -33600,18 +33608,98 @@
       <c r="P200" t="n">
         <v>0</v>
       </c>
-      <c r="R200" t="n">
-        <v>0</v>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN200" t="b">
+        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -33705,17 +33793,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -33749,173 +33837,81 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O201" t="n">
-        <v>0</v>
-      </c>
-      <c r="P201" t="n">
-        <v>0</v>
-      </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
         <v>1</v>
       </c>
+      <c r="R201" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33947,12 +33943,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -33977,7 +33973,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -33991,6 +33987,9 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -33999,68 +33998,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34087,7 +34095,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -34122,7 +34130,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -34131,26 +34139,106 @@
         </is>
       </c>
       <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
         <v>1</v>
-      </c>
-      <c r="O203" t="n">
-        <v>1</v>
-      </c>
-      <c r="P203" t="n">
-        <v>1</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -34244,17 +34332,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -34288,173 +34376,81 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
-        <v>1</v>
-      </c>
-      <c r="P204" t="n">
-        <v>1</v>
-      </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34486,12 +34482,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -34516,90 +34512,102 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O205" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P205" t="n">
+        <v>1</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34626,123 +34634,505 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>1</v>
+      </c>
+      <c r="O206" t="n">
+        <v>1</v>
+      </c>
+      <c r="P206" t="n">
+        <v>1</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA206" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
+      <c r="AT207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA207" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
+      <c r="G208" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>D002</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
         <is>
           <t>霍乱</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
+      <c r="K208" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
+      <c r="L208" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr">
+      <c r="M208" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N206" t="n">
-        <v>0</v>
-      </c>
-      <c r="O206" t="n">
-        <v>0</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0</v>
-      </c>
-      <c r="S206" t="inlineStr">
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO206" t="inlineStr">
+      <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP206" t="inlineStr">
+      <c r="AP208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR206" t="inlineStr">
+      <c r="AR208" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS206" t="inlineStr"/>
-      <c r="AT206" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU206" t="inlineStr">
+      <c r="AS208" t="inlineStr"/>
+      <c r="AT208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU208" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV206" t="inlineStr">
+      <c r="AV208" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW206" t="inlineStr">
+      <c r="AW208" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX206" t="inlineStr">
+      <c r="AX208" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY206" t="inlineStr">
+      <c r="AY208" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ206" t="inlineStr">
+      <c r="AZ208" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA206" t="inlineStr">
+      <c r="BA208" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB206" t="inlineStr">
+      <c r="BB208" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC206" t="inlineStr">
+      <c r="BC208" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -34864,7 +35254,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10">
@@ -34874,7 +35264,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -34894,7 +35284,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -35138,6 +35138,151 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
+      <c r="AT209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35171,7 +35316,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -35254,7 +35399,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10">
@@ -35264,7 +35409,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -35283,6 +35283,400 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA210" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35399,7 +35793,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
@@ -35409,7 +35803,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -35429,7 +35823,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -32036,12 +32036,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -32114,42 +32114,42 @@
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -32181,12 +32181,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -32211,7 +32211,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -32259,42 +32259,42 @@
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -32326,12 +32326,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -32370,9 +32370,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="P193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -32381,77 +32378,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32478,7 +32466,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -32530,98 +32518,18 @@
       <c r="P194" t="n">
         <v>0</v>
       </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN194" t="b">
-        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -32715,17 +32623,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -32750,7 +32658,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -32764,76 +32672,168 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="R195" t="n">
-        <v>0</v>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
+        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32865,12 +32865,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -32909,9 +32909,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="P196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -32920,77 +32917,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33017,7 +33005,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -33069,98 +33057,18 @@
       <c r="P197" t="n">
         <v>0</v>
       </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD197" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE197" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN197" t="b">
-        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
@@ -33254,17 +33162,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -33289,7 +33197,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -33303,76 +33211,168 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="R198" t="n">
-        <v>0</v>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN198" t="b">
+        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33404,12 +33404,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -33448,9 +33448,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="P199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -33459,77 +33456,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33556,7 +33544,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -33608,98 +33596,18 @@
       <c r="P200" t="n">
         <v>0</v>
       </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -33793,17 +33701,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -33828,7 +33736,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -33837,81 +33745,173 @@
         </is>
       </c>
       <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
         <v>1</v>
       </c>
-      <c r="O201" t="n">
-        <v>1</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33943,12 +33943,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -33982,93 +33982,81 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O202" t="n">
-        <v>0</v>
-      </c>
-      <c r="P202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R202" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34095,7 +34083,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -34147,98 +34135,18 @@
       <c r="P203" t="n">
         <v>0</v>
       </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -34332,17 +34240,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -34367,7 +34275,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -34381,76 +34289,168 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="R204" t="n">
-        <v>0</v>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
+        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34482,12 +34482,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -34521,93 +34521,81 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
-        <v>1</v>
-      </c>
-      <c r="P205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34634,7 +34622,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -34686,98 +34674,18 @@
       <c r="P206" t="n">
         <v>1</v>
       </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R206" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
@@ -34871,17 +34779,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -34906,90 +34814,182 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P207" t="n">
+        <v>1</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35021,12 +35021,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -35099,42 +35099,42 @@
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35166,12 +35166,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -35196,7 +35196,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -35244,42 +35244,42 @@
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35311,12 +35311,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -35355,9 +35355,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="P210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -35366,77 +35363,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA210" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ210" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35463,7 +35451,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -35515,98 +35503,18 @@
       <c r="P211" t="n">
         <v>0</v>
       </c>
-      <c r="U211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W211" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X211" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y211" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD211" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE211" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF211" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG211" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH211" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI211" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ211" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK211" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM211" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN211" t="b">
-        <v>1</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
@@ -35672,6 +35580,782 @@
         </is>
       </c>
       <c r="BC211" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
+      <c r="AT213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV214" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA214" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB214" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC214" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN215" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -35710,7 +36394,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -35793,7 +36477,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -35803,7 +36487,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -35823,7 +36507,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -47246,6 +47246,690 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>0</v>
+      </c>
+      <c r="O272" t="n">
+        <v>0</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr"/>
+      <c r="AT272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV272" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA272" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB272" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC272" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" t="n">
+        <v>0</v>
+      </c>
+      <c r="R273" t="n">
+        <v>0</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV273" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA273" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB273" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC273" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" t="n">
+        <v>0</v>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ274" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM274" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN274" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" t="n">
+        <v>0</v>
+      </c>
+      <c r="R275" t="n">
+        <v>0</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr"/>
+      <c r="AT275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV275" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA275" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB275" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC275" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47279,7 +47963,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -47362,7 +48046,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -47372,7 +48056,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -47392,7 +48076,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2474,6 +2519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3009,6 +3059,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3154,6 +3209,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3302,6 +3362,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3992,6 +4057,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4682,6 +4752,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5372,6 +5447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6062,6 +6142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6210,6 +6295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6355,6 +6445,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6500,6 +6595,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6645,6 +6745,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6790,6 +6895,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6935,6 +7045,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7080,6 +7195,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7216,6 +7336,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7361,6 +7486,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7899,6 +8029,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8434,6 +8569,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8579,6 +8719,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9269,6 +9414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9959,6 +10109,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10649,6 +10804,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11339,6 +11499,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11487,6 +11652,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11632,6 +11802,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11777,6 +11952,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11922,6 +12102,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12067,6 +12252,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12212,6 +12402,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12357,6 +12552,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12502,6 +12702,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12647,6 +12852,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13185,6 +13395,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13330,6 +13545,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13475,6 +13695,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14165,6 +14390,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14855,6 +15085,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15545,6 +15780,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16235,6 +16475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16774,6 +17019,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16919,6 +17169,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17064,6 +17319,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17209,6 +17469,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17354,6 +17619,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17499,6 +17769,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17644,6 +17919,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17789,6 +18069,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17934,6 +18219,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18472,6 +18762,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18617,6 +18912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18762,6 +19062,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19058,6 +19363,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19748,6 +20058,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20438,6 +20753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21128,6 +21448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21667,6 +21992,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21812,6 +22142,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21957,6 +22292,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22102,6 +22442,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22247,6 +22592,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22392,6 +22742,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22537,6 +22892,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22682,6 +23042,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22827,6 +23192,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23365,6 +23735,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24290,6 +24665,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24435,6 +24815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24731,6 +25116,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25421,6 +25811,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26111,6 +26506,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26801,6 +27201,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27491,6 +27896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28030,6 +28440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28175,6 +28590,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28320,6 +28740,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28465,6 +28890,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28610,6 +29040,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28755,6 +29190,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28900,6 +29340,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29045,6 +29490,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29190,6 +29640,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29728,6 +30183,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32983,6 +33443,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33128,6 +33593,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33563,6 +34033,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34247,6 +34722,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34931,6 +35411,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35615,6 +36100,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36154,6 +36644,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36299,6 +36794,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36444,6 +36944,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36589,6 +37094,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36734,6 +37244,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36879,6 +37394,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37024,6 +37544,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37169,6 +37694,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37314,6 +37844,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37852,6 +38387,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41492,6 +42032,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41637,6 +42182,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41927,6 +42477,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42611,6 +43166,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43295,6 +43855,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43979,6 +44544,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44663,6 +45233,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44808,6 +45383,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44953,6 +45533,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45098,6 +45683,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45243,6 +45833,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45388,6 +45983,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45533,6 +46133,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45678,6 +46283,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45823,6 +46433,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45916,12 +46531,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -45955,84 +46570,92 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O272" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
-      <c r="R272" t="n">
-        <v>0.0002123271347081624</v>
+        <v>0</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR272" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46059,17 +46682,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -46108,14 +46731,34 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_CHOLERA</t>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -46123,6 +46766,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary cholera notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46140,7 +46841,7 @@
       </c>
       <c r="AS273" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_CHOLERA</t>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
         </is>
       </c>
       <c r="AT273" t="n">
@@ -46153,42 +46854,42 @@
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46215,17 +46916,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -46259,39 +46960,20 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O274" t="n">
-        <v>0</v>
-      </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X274" t="inlineStr">
-        <is>
-          <t>霍乱</t>
-        </is>
-      </c>
-      <c r="Y274" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        <v>3</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>0</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0.0002123271347081624</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -46299,130 +46981,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>country:CN-CQ:national</t>
-        </is>
-      </c>
-      <c r="AD274" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE274" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF274" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG274" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ274" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK274" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM274" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN274" t="b">
-        <v>1</v>
-      </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ274" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS274" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr"/>
       <c r="AT274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -46454,12 +47074,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -46573,7 +47193,7 @@
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
@@ -46610,12 +47230,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -46696,7 +47316,7 @@
       </c>
       <c r="AC276" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD276" t="inlineStr">
@@ -46807,7 +47427,7 @@
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
@@ -46844,12 +47464,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -46893,6 +47513,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CHOLERA</t>
+        </is>
+      </c>
       <c r="AA277" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46905,7 +47530,7 @@
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ277" t="inlineStr">
@@ -46915,15 +47540,15 @@
       </c>
       <c r="AS277" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_CHOLERA; SER_CN_PROV_REPORT_CHOLERA</t>
+          <t>SER_CN_PROV_REPORT_CHOLERA</t>
         </is>
       </c>
       <c r="AT277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
@@ -46958,7 +47583,7 @@
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
@@ -46995,12 +47620,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -47081,7 +47706,7 @@
       </c>
       <c r="AC278" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD278" t="inlineStr">
@@ -47139,7 +47764,7 @@
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ278" t="inlineStr">
@@ -47149,15 +47774,15 @@
       </c>
       <c r="AS278" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_CHOLERA; SER_CN_PROV_REPORT_CHOLERA</t>
+          <t>SER_CN_PROV_REPORT_CHOLERA</t>
         </is>
       </c>
       <c r="AT278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
@@ -47192,7 +47817,7 @@
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
@@ -47229,12 +47854,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -47268,10 +47893,10 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -47343,7 +47968,7 @@
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
@@ -47380,12 +48005,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -47419,10 +48044,10 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U280" t="inlineStr">
         <is>
@@ -47466,7 +48091,7 @@
       </c>
       <c r="AC280" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD280" t="inlineStr">
@@ -47577,7 +48202,7 @@
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
@@ -47614,12 +48239,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -47653,21 +48278,16 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_CHOLERA</t>
-        </is>
-      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47680,7 +48300,7 @@
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ281" t="inlineStr">
@@ -47690,15 +48310,15 @@
       </c>
       <c r="AS281" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_CHOLERA</t>
+          <t>SER_CN_PROV_DC_CHOLERA; SER_CN_PROV_REPORT_CHOLERA</t>
         </is>
       </c>
       <c r="AT281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV281" t="inlineStr">
@@ -47733,7 +48353,7 @@
       </c>
       <c r="BB281" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC281" t="inlineStr">
@@ -47770,12 +48390,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -47809,10 +48429,10 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U282" t="inlineStr">
         <is>
@@ -47856,7 +48476,7 @@
       </c>
       <c r="AC282" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD282" t="inlineStr">
@@ -47914,7 +48534,7 @@
       </c>
       <c r="AP282" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ282" t="inlineStr">
@@ -47924,15 +48544,15 @@
       </c>
       <c r="AS282" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_CHOLERA</t>
+          <t>SER_CN_PROV_DC_CHOLERA; SER_CN_PROV_REPORT_CHOLERA</t>
         </is>
       </c>
       <c r="AT282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV282" t="inlineStr">
@@ -47967,7 +48587,7 @@
       </c>
       <c r="BB282" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC282" t="inlineStr">
@@ -48004,12 +48624,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -48123,7 +48743,7 @@
       </c>
       <c r="BB283" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC283" t="inlineStr">
@@ -48160,12 +48780,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -48246,7 +48866,7 @@
       </c>
       <c r="AC284" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD284" t="inlineStr">
@@ -48357,7 +48977,7 @@
       </c>
       <c r="BB284" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC284" t="inlineStr">
@@ -48394,12 +49014,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -48513,7 +49133,7 @@
       </c>
       <c r="BB285" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC285" t="inlineStr">
@@ -48550,12 +49170,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -48636,7 +49256,7 @@
       </c>
       <c r="AC286" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD286" t="inlineStr">
@@ -48747,7 +49367,7 @@
       </c>
       <c r="BB286" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC286" t="inlineStr">
@@ -48784,12 +49404,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -48828,76 +49448,87 @@
       <c r="O287" t="n">
         <v>0</v>
       </c>
-      <c r="R287" t="n">
-        <v>0</v>
-      </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO287" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR287" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS287" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV287" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA287" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB287" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC287" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48924,17 +49555,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -48973,76 +49604,165 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="R288" t="n">
-        <v>0</v>
-      </c>
-      <c r="S288" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ288" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK288" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM288" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN288" t="b">
+        <v>1</v>
       </c>
       <c r="AO288" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR288" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS288" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA288" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB288" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC288" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -49074,12 +49794,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -49104,7 +49824,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -49124,6 +49844,11 @@
       <c r="S289" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO289" t="inlineStr">
@@ -49152,42 +49877,42 @@
       </c>
       <c r="AV289" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ289" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA289" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB289" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC289" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -49219,12 +49944,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -49249,7 +49974,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -49263,9 +49988,6 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
-      <c r="P290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
@@ -49276,75 +49998,71 @@
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO290" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP290" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ290" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS290" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR290" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr"/>
       <c r="AT290" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV290" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ290" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA290" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB290" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC290" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -49371,17 +50089,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -49420,168 +50138,76 @@
       <c r="O291" t="n">
         <v>0</v>
       </c>
-      <c r="P291" t="n">
-        <v>0</v>
-      </c>
-      <c r="U291" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V291" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W291" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X291" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y291" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z291" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA291" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB291" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC291" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD291" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE291" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF291" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG291" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH291" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI291" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ291" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK291" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM291" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN291" t="b">
-        <v>1</v>
+      <c r="R291" t="n">
+        <v>0</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO291" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP291" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ291" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS291" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR291" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr"/>
       <c r="AT291" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV291" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ291" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA291" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB291" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC291" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49613,12 +50239,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -49643,7 +50269,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -49657,6 +50283,9 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
+      <c r="P292" t="n">
+        <v>0</v>
+      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -49665,68 +50294,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP292" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR292" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS292" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ292" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS292" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT292" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV292" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ292" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA292" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB292" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC292" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -49753,7 +50391,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -49788,7 +50426,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -49805,18 +50443,98 @@
       <c r="P293" t="n">
         <v>0</v>
       </c>
-      <c r="R293" t="n">
-        <v>0</v>
-      </c>
-      <c r="S293" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC293" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD293" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF293" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG293" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH293" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI293" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ293" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK293" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM293" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN293" t="b">
+        <v>1</v>
       </c>
       <c r="AO293" t="inlineStr">
         <is>
@@ -49910,17 +50628,17 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -49959,168 +50677,76 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="P294" t="n">
-        <v>0</v>
-      </c>
-      <c r="U294" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V294" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W294" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X294" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y294" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z294" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA294" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB294" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC294" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD294" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE294" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF294" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG294" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH294" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI294" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ294" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK294" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM294" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN294" t="b">
-        <v>1</v>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO294" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ294" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS294" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR294" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr"/>
       <c r="AT294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV294" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ294" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA294" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB294" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC294" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -50152,12 +50778,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -50182,7 +50808,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -50196,6 +50822,9 @@
       <c r="O295" t="n">
         <v>0</v>
       </c>
+      <c r="P295" t="n">
+        <v>0</v>
+      </c>
       <c r="R295" t="n">
         <v>0</v>
       </c>
@@ -50204,68 +50833,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP295" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR295" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS295" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ295" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS295" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT295" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV295" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ295" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA295" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB295" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC295" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -50292,7 +50930,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -50327,7 +50965,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -50344,18 +50982,98 @@
       <c r="P296" t="n">
         <v>0</v>
       </c>
-      <c r="R296" t="n">
-        <v>0</v>
-      </c>
-      <c r="S296" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC296" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD296" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE296" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF296" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG296" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH296" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI296" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ296" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK296" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM296" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN296" t="b">
+        <v>1</v>
       </c>
       <c r="AO296" t="inlineStr">
         <is>
@@ -50449,17 +51167,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -50498,168 +51216,76 @@
       <c r="O297" t="n">
         <v>0</v>
       </c>
-      <c r="P297" t="n">
-        <v>0</v>
-      </c>
-      <c r="U297" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V297" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W297" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X297" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y297" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z297" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA297" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB297" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC297" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD297" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE297" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF297" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG297" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH297" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI297" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ297" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK297" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM297" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN297" t="b">
-        <v>1</v>
+      <c r="R297" t="n">
+        <v>0</v>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO297" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP297" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ297" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS297" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR297" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS297" t="inlineStr"/>
       <c r="AT297" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV297" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ297" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA297" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB297" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC297" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -50691,12 +51317,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -50721,7 +51347,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -50730,81 +51356,93 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O298" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P298" t="n">
+        <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S298" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP298" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR298" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS298" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ298" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS298" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT298" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA298" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -50831,7 +51469,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -50866,7 +51504,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -50883,18 +51521,98 @@
       <c r="P299" t="n">
         <v>0</v>
       </c>
-      <c r="R299" t="n">
-        <v>0</v>
-      </c>
-      <c r="S299" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF299" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH299" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI299" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ299" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK299" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM299" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN299" t="b">
+        <v>1</v>
       </c>
       <c r="AO299" t="inlineStr">
         <is>
@@ -50988,17 +51706,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -51032,173 +51750,81 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O300" t="n">
-        <v>0</v>
-      </c>
-      <c r="P300" t="n">
-        <v>0</v>
-      </c>
-      <c r="U300" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V300" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W300" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X300" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y300" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z300" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA300" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB300" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC300" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD300" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE300" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF300" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG300" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH300" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI300" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ300" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK300" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM300" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN300" t="b">
         <v>1</v>
       </c>
+      <c r="R300" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ300" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS300" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR300" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS300" t="inlineStr"/>
       <c r="AT300" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -51230,12 +51856,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -51260,7 +51886,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -51274,6 +51900,9 @@
       <c r="O301" t="n">
         <v>0</v>
       </c>
+      <c r="P301" t="n">
+        <v>0</v>
+      </c>
       <c r="R301" t="n">
         <v>0</v>
       </c>
@@ -51282,68 +51911,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP301" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR301" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS301" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ301" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS301" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV301" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA301" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB301" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC301" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -51370,7 +52008,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -51405,7 +52043,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -51414,26 +52052,106 @@
         </is>
       </c>
       <c r="N302" t="n">
+        <v>0</v>
+      </c>
+      <c r="O302" t="n">
+        <v>0</v>
+      </c>
+      <c r="P302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD302" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF302" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH302" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI302" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ302" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK302" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM302" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN302" t="b">
         <v>1</v>
-      </c>
-      <c r="O302" t="n">
-        <v>1</v>
-      </c>
-      <c r="P302" t="n">
-        <v>1</v>
-      </c>
-      <c r="R302" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA302" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO302" t="inlineStr">
         <is>
@@ -51527,17 +52245,17 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -51571,173 +52289,81 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O303" t="n">
-        <v>1</v>
-      </c>
-      <c r="P303" t="n">
-        <v>1</v>
-      </c>
-      <c r="U303" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V303" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W303" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X303" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y303" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z303" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA303" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB303" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC303" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD303" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE303" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF303" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG303" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH303" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI303" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ303" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK303" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM303" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN303" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R303" t="n">
+        <v>0</v>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO303" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ303" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS303" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR303" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS303" t="inlineStr"/>
       <c r="AT303" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -51769,12 +52395,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -51799,90 +52425,102 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O304" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P304" t="n">
+        <v>1</v>
       </c>
       <c r="R304" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP304" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR304" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS304" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ304" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS304" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT304" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV304" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA304" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB304" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC304" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -51909,17 +52547,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -51944,90 +52582,182 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O305" t="n">
-        <v>0</v>
-      </c>
-      <c r="R305" t="n">
-        <v>0</v>
-      </c>
-      <c r="S305" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P305" t="n">
+        <v>1</v>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC305" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD305" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF305" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG305" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH305" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI305" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ305" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK305" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM305" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN305" t="b">
+        <v>1</v>
       </c>
       <c r="AO305" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP305" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR305" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS305" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ305" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS305" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT305" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV305" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ305" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA305" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB305" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC305" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -52059,12 +52789,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -52108,7 +52838,12 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO306" t="inlineStr">
@@ -52142,12 +52877,12 @@
       </c>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
@@ -52162,12 +52897,12 @@
       </c>
       <c r="BA306" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB306" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC306" t="inlineStr">
@@ -52204,12 +52939,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -52254,6 +52989,11 @@
       <c r="S307" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO307" t="inlineStr">
@@ -52287,7 +53027,7 @@
       </c>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
@@ -52307,7 +53047,7 @@
       </c>
       <c r="BA307" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB307" t="inlineStr">
@@ -52349,12 +53089,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -52399,6 +53139,11 @@
       <c r="S308" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO308" t="inlineStr">
@@ -52432,7 +53177,7 @@
       </c>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
@@ -52452,7 +53197,7 @@
       </c>
       <c r="BA308" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB308" t="inlineStr">
@@ -52494,12 +53239,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -52544,6 +53289,11 @@
       <c r="S309" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO309" t="inlineStr">
@@ -52577,7 +53327,7 @@
       </c>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
@@ -52597,7 +53347,7 @@
       </c>
       <c r="BA309" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB309" t="inlineStr">
@@ -52639,12 +53389,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -52689,6 +53439,11 @@
       <c r="S310" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO310" t="inlineStr">
@@ -52722,7 +53477,7 @@
       </c>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
@@ -52742,7 +53497,7 @@
       </c>
       <c r="BA310" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB310" t="inlineStr">
@@ -52784,12 +53539,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -52834,6 +53589,11 @@
       <c r="S311" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO311" t="inlineStr">
@@ -52867,7 +53627,7 @@
       </c>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
@@ -52887,7 +53647,7 @@
       </c>
       <c r="BA311" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB311" t="inlineStr">
@@ -52929,12 +53689,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -52979,6 +53739,11 @@
       <c r="S312" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO312" t="inlineStr">
@@ -53012,7 +53777,7 @@
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
@@ -53032,7 +53797,7 @@
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
@@ -53074,12 +53839,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -53123,7 +53888,12 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO313" t="inlineStr">
@@ -53152,42 +53922,42 @@
       </c>
       <c r="AV313" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ313" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA313" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB313" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC313" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -53219,12 +53989,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -53249,7 +54019,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -53268,7 +54038,12 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO314" t="inlineStr">
@@ -53297,42 +54072,42 @@
       </c>
       <c r="AV314" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ314" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA314" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB314" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC314" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -53364,12 +54139,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -53394,7 +54169,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -53408,9 +54183,6 @@
       <c r="O315" t="n">
         <v>0</v>
       </c>
-      <c r="P315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0</v>
       </c>
@@ -53421,75 +54193,71 @@
       </c>
       <c r="AA315" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO315" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP315" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ315" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS315" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr"/>
       <c r="AT315" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV315" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA315" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -53516,17 +54284,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -53565,168 +54333,76 @@
       <c r="O316" t="n">
         <v>0</v>
       </c>
-      <c r="P316" t="n">
-        <v>0</v>
-      </c>
-      <c r="U316" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V316" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W316" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X316" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y316" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z316" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA316" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB316" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC316" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD316" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE316" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF316" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG316" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH316" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI316" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ316" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK316" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM316" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN316" t="b">
-        <v>1</v>
+      <c r="R316" t="n">
+        <v>0</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO316" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP316" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ316" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS316" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR316" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr"/>
       <c r="AT316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV316" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ316" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA316" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB316" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC316" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -53758,12 +54434,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -53788,7 +54464,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -53802,6 +54478,9 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
+      <c r="P317" t="n">
+        <v>0</v>
+      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -53810,68 +54489,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP317" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR317" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS317" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT317" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU317" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV317" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ317" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA317" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB317" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC317" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -53898,7 +54586,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -53933,7 +54621,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -53950,18 +54638,98 @@
       <c r="P318" t="n">
         <v>0</v>
       </c>
-      <c r="R318" t="n">
-        <v>0</v>
-      </c>
-      <c r="S318" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ318" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK318" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM318" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN318" t="b">
+        <v>1</v>
       </c>
       <c r="AO318" t="inlineStr">
         <is>
@@ -54055,17 +54823,17 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -54104,168 +54872,76 @@
       <c r="O319" t="n">
         <v>0</v>
       </c>
-      <c r="P319" t="n">
-        <v>0</v>
-      </c>
-      <c r="U319" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V319" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W319" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X319" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y319" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z319" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA319" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB319" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC319" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD319" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE319" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF319" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG319" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH319" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI319" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ319" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK319" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM319" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN319" t="b">
-        <v>1</v>
+      <c r="R319" t="n">
+        <v>0</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO319" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP319" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ319" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS319" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr"/>
       <c r="AT319" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU319" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV319" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW319" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ319" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA319" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB319" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC319" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54297,12 +54973,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -54327,7 +55003,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -54341,6 +55017,9 @@
       <c r="O320" t="n">
         <v>0</v>
       </c>
+      <c r="P320" t="n">
+        <v>0</v>
+      </c>
       <c r="R320" t="n">
         <v>0</v>
       </c>
@@ -54349,68 +55028,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP320" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR320" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS320" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ320" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT320" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV320" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ320" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA320" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB320" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC320" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -54437,7 +55125,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -54472,7 +55160,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -54489,18 +55177,98 @@
       <c r="P321" t="n">
         <v>0</v>
       </c>
-      <c r="R321" t="n">
-        <v>0</v>
-      </c>
-      <c r="S321" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ321" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK321" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM321" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN321" t="b">
+        <v>1</v>
       </c>
       <c r="AO321" t="inlineStr">
         <is>
@@ -54594,17 +55362,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -54643,168 +55411,76 @@
       <c r="O322" t="n">
         <v>0</v>
       </c>
-      <c r="P322" t="n">
-        <v>0</v>
-      </c>
-      <c r="U322" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V322" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W322" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X322" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y322" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA322" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB322" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC322" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD322" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE322" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF322" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG322" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH322" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI322" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ322" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK322" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM322" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN322" t="b">
-        <v>1</v>
+      <c r="R322" t="n">
+        <v>0</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO322" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP322" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ322" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS322" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR322" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr"/>
       <c r="AT322" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU322" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV322" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ322" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA322" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB322" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC322" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54836,12 +55512,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -54866,7 +55542,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -54880,6 +55556,9 @@
       <c r="O323" t="n">
         <v>0</v>
       </c>
+      <c r="P323" t="n">
+        <v>0</v>
+      </c>
       <c r="R323" t="n">
         <v>0</v>
       </c>
@@ -54888,68 +55567,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP323" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR323" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS323" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ323" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS323" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT323" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU323" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV323" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ323" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA323" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB323" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC323" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -54976,123 +55664,904 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N324" t="n">
+        <v>0</v>
+      </c>
+      <c r="O324" t="n">
+        <v>0</v>
+      </c>
+      <c r="P324" t="n">
+        <v>0</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ324" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK324" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM324" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN324" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO324" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP324" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ324" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS324" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT324" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU324" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV324" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW324" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX324" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY324" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA324" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB324" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC324" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr">
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N325" t="n">
+        <v>0</v>
+      </c>
+      <c r="O325" t="n">
+        <v>0</v>
+      </c>
+      <c r="R325" t="n">
+        <v>0</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO325" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP325" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR325" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS325" t="inlineStr"/>
+      <c r="AT325" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU325" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV325" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW325" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX325" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY325" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA325" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB325" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC325" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N326" t="n">
+        <v>0</v>
+      </c>
+      <c r="O326" t="n">
+        <v>0</v>
+      </c>
+      <c r="P326" t="n">
+        <v>0</v>
+      </c>
+      <c r="R326" t="n">
+        <v>0</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO326" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP326" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ326" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS326" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT326" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU326" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV326" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW326" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX326" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY326" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA326" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB326" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC326" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N327" t="n">
+        <v>0</v>
+      </c>
+      <c r="O327" t="n">
+        <v>0</v>
+      </c>
+      <c r="P327" t="n">
+        <v>0</v>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ327" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK327" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM327" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN327" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO327" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP327" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ327" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS327" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT327" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU327" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV327" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW327" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX327" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY327" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA327" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB327" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC327" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr">
+      <c r="G328" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>D002</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="J324" t="inlineStr">
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
         <is>
           <t>霍乱</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr">
+      <c r="K328" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr">
+      <c r="L328" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M324" t="inlineStr">
+      <c r="M328" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N324" t="n">
-        <v>0</v>
-      </c>
-      <c r="O324" t="n">
-        <v>0</v>
-      </c>
-      <c r="R324" t="n">
-        <v>0</v>
-      </c>
-      <c r="S324" t="inlineStr">
+      <c r="N328" t="n">
+        <v>0</v>
+      </c>
+      <c r="O328" t="n">
+        <v>0</v>
+      </c>
+      <c r="R328" t="n">
+        <v>0</v>
+      </c>
+      <c r="S328" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO324" t="inlineStr">
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO328" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP324" t="inlineStr">
+      <c r="AP328" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR324" t="inlineStr">
+      <c r="AR328" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS324" t="inlineStr"/>
-      <c r="AT324" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU324" t="inlineStr">
+      <c r="AS328" t="inlineStr"/>
+      <c r="AT328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU328" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV324" t="inlineStr">
+      <c r="AV328" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW324" t="inlineStr">
+      <c r="AW328" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX324" t="inlineStr">
+      <c r="AX328" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY324" t="inlineStr">
+      <c r="AY328" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ324" t="inlineStr">
+      <c r="AZ328" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA324" t="inlineStr">
+      <c r="BA328" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB324" t="inlineStr">
+      <c r="BB328" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC324" t="inlineStr">
+      <c r="BC328" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -55214,7 +56683,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -55224,7 +56693,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11">
@@ -55244,7 +56713,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -56567,6 +56567,151 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N329" t="n">
+        <v>0</v>
+      </c>
+      <c r="O329" t="n">
+        <v>0</v>
+      </c>
+      <c r="R329" t="n">
+        <v>0</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO329" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP329" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR329" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS329" t="inlineStr"/>
+      <c r="AT329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU329" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV329" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW329" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX329" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY329" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA329" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB329" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC329" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56600,7 +56745,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -56683,7 +56828,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -56693,7 +56838,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11">
